--- a/input/mapping/051. OCB_GOLD_TCKH_V_FTP_INTEREST_RATE_NIM_ON_PHAT.xlsx
+++ b/input/mapping/051. OCB_GOLD_TCKH_V_FTP_INTEREST_RATE_NIM_ON_PHAT.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OCB\Zone_C\Code dev lại silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="573" documentId="13_ncr:1_{59B91070-12FC-497E-8E29-8A77D2FCFAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7835747-315D-490F-9D71-CBA793DB89FF}"/>
+  <xr:revisionPtr revIDLastSave="584" documentId="13_ncr:1_{59B91070-12FC-497E-8E29-8A77D2FCFAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58105EFC-D417-4E04-9E85-7A631E00F9AF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Script" sheetId="11" r:id="rId2"/>
     <sheet name="V_FTP_INTEREST_RATE_NIM_ON" sheetId="3" r:id="rId3"/>
-    <sheet name="FTP_RATE_LIST_HIST" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>V_FTP_INTEREST_RATE_NIM_ON —  Data Lineage Summary</t>
   </si>
@@ -115,7 +114,7 @@
     INT_RATE_TYPE,
     CURRENCY,
     RATE
-FROM FTP_RATE_LIST_HIST
+FROM IDENTIFIER(:curated || '.ocbftp.ftp_rate_list_hist')
 WHERE TERM = 'ON'
   AND INTEREST_KEY_ID = 1
   AND INT_RATE_TYPE = 'BUY';</t>
@@ -177,55 +176,6 @@
   </si>
   <si>
     <t>RATE</t>
-  </si>
-  <si>
-    <t>FTP_RATE_LIST_HIST — VIEW
-JOIN SCHEMA — FTP_RATE_LIST_HIST</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — FTP_RATE_LIST_HIST</t>
-  </si>
-  <si>
-    <t>Data Type</t>
-  </si>
-  <si>
-    <t>LAST_UPDATED</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>USER_APPROVED</t>
-  </si>
-  <si>
-    <t>STRING</t>
-  </si>
-  <si>
-    <t>USER_CREATED</t>
-  </si>
-  <si>
-    <t>DAYS_TO</t>
-  </si>
-  <si>
-    <t>BIGINT</t>
-  </si>
-  <si>
-    <t>DAYS_FROM</t>
-  </si>
-  <si>
-    <t>TERM</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>DECIMAL(12,6)</t>
-  </si>
-  <si>
-    <t>LAST_DATE_CHANGE</t>
-  </si>
-  <si>
-    <t>INTEREST_KEY_ID</t>
   </si>
 </sst>
 </file>
@@ -335,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -359,21 +309,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF1A1A6E"/>
       </left>
@@ -572,33 +507,24 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,28 +533,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -637,88 +551,85 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1049,33 +960,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="27"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
     </row>
     <row r="2" spans="1:25" ht="6" customHeight="1"/>
     <row r="3" spans="1:25" ht="7.15" customHeight="1">
@@ -1090,43 +1001,43 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="37" t="s">
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="30"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="33"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:25" ht="19.899999999999999" customHeight="1">
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:25" ht="7.15" customHeight="1">
       <c r="B7" s="3"/>
@@ -1239,609 +1150,609 @@
   <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="236.140625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="53"/>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
+      <c r="A1" s="48"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="2" spans="1:3" ht="18.75">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.75">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.75">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="53"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="53"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="A7" s="48"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="53"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="53"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="53"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
+      <c r="A24" s="48"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
+      <c r="A25" s="48"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
+      <c r="A28" s="48"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="53"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="53"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="53"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
+      <c r="A32" s="48"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="53"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="53"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
+      <c r="A34" s="48"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
+      <c r="A35" s="48"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
+      <c r="A36" s="48"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="53"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
+      <c r="A37" s="48"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="53"/>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
+      <c r="A38" s="48"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="53"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
+      <c r="A39" s="48"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="53"/>
-      <c r="B40" s="54"/>
-      <c r="C40" s="54"/>
+      <c r="A40" s="48"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="53"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
+      <c r="A41" s="48"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="53"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
+      <c r="A42" s="48"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="53"/>
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
+      <c r="A43" s="48"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="53"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="54"/>
+      <c r="A44" s="48"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="53"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
+      <c r="A45" s="48"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="53"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="54"/>
+      <c r="A46" s="48"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="53"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
+      <c r="A47" s="48"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="53"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
+      <c r="A48" s="48"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="53"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
+      <c r="A49" s="48"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="53"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
+      <c r="A50" s="48"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="53"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
+      <c r="A51" s="48"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="53"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
+      <c r="A52" s="48"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="53"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="48"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="49"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="53"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
+      <c r="A54" s="48"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="49"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="53"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
+      <c r="A55" s="48"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
+      <c r="A56" s="48"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
+      <c r="A57" s="48"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="53"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
+      <c r="A58" s="48"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="53"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
+      <c r="A59" s="48"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="53"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
+      <c r="A60" s="48"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="53"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
+      <c r="A61" s="48"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="53"/>
-      <c r="B62" s="54"/>
-      <c r="C62" s="54"/>
+      <c r="A62" s="48"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="53"/>
-      <c r="B63" s="54"/>
-      <c r="C63" s="54"/>
+      <c r="A63" s="48"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="53"/>
-      <c r="B64" s="54"/>
-      <c r="C64" s="54"/>
+      <c r="A64" s="48"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="53"/>
-      <c r="B65" s="54"/>
-      <c r="C65" s="54"/>
+      <c r="A65" s="48"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="49"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="53"/>
-      <c r="B66" s="54"/>
-      <c r="C66" s="54"/>
+      <c r="A66" s="48"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="49"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="53"/>
-      <c r="B67" s="54"/>
-      <c r="C67" s="54"/>
+      <c r="A67" s="48"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="53"/>
-      <c r="B68" s="54"/>
-      <c r="C68" s="54"/>
+      <c r="A68" s="48"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="53"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="54"/>
+      <c r="A69" s="48"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="53"/>
-      <c r="B70" s="54"/>
-      <c r="C70" s="54"/>
+      <c r="A70" s="48"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="53"/>
-      <c r="B71" s="54"/>
-      <c r="C71" s="54"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="53"/>
-      <c r="B72" s="54"/>
-      <c r="C72" s="54"/>
+      <c r="A72" s="48"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="53"/>
-      <c r="B73" s="54"/>
-      <c r="C73" s="54"/>
+      <c r="A73" s="48"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="53"/>
-      <c r="B74" s="54"/>
-      <c r="C74" s="54"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="53"/>
-      <c r="B75" s="54"/>
-      <c r="C75" s="54"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="53"/>
-      <c r="B76" s="54"/>
-      <c r="C76" s="54"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="53"/>
-      <c r="B77" s="54"/>
-      <c r="C77" s="54"/>
+      <c r="A77" s="48"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="49"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="53"/>
-      <c r="B78" s="54"/>
-      <c r="C78" s="54"/>
+      <c r="A78" s="48"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="53"/>
-      <c r="B79" s="54"/>
-      <c r="C79" s="54"/>
+      <c r="A79" s="48"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="53"/>
-      <c r="B80" s="54"/>
-      <c r="C80" s="54"/>
+      <c r="A80" s="48"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="53"/>
-      <c r="B81" s="54"/>
-      <c r="C81" s="54"/>
+      <c r="A81" s="48"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="49"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="53"/>
-      <c r="B82" s="54"/>
-      <c r="C82" s="54"/>
+      <c r="A82" s="48"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="49"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="53"/>
-      <c r="B83" s="54"/>
-      <c r="C83" s="54"/>
+      <c r="A83" s="48"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="53"/>
-      <c r="B84" s="54"/>
-      <c r="C84" s="54"/>
+      <c r="A84" s="48"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="53"/>
-      <c r="B85" s="54"/>
-      <c r="C85" s="54"/>
+      <c r="A85" s="48"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="49"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="53"/>
-      <c r="B86" s="54"/>
-      <c r="C86" s="54"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="53"/>
-      <c r="B87" s="54"/>
-      <c r="C87" s="54"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="53"/>
-      <c r="B88" s="54"/>
-      <c r="C88" s="54"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="53"/>
-      <c r="B89" s="54"/>
-      <c r="C89" s="54"/>
+      <c r="A89" s="48"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="53"/>
-      <c r="B90" s="54"/>
-      <c r="C90" s="54"/>
+      <c r="A90" s="48"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="49"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="53"/>
-      <c r="B91" s="54"/>
-      <c r="C91" s="54"/>
+      <c r="A91" s="48"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="49"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="53"/>
-      <c r="B92" s="54"/>
-      <c r="C92" s="54"/>
+      <c r="A92" s="48"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="49"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="53"/>
-      <c r="B93" s="54"/>
-      <c r="C93" s="54"/>
+      <c r="A93" s="48"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="49"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="53"/>
-      <c r="B94" s="54"/>
-      <c r="C94" s="54"/>
+      <c r="A94" s="48"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="49"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="53"/>
-      <c r="B95" s="54"/>
-      <c r="C95" s="54"/>
+      <c r="A95" s="48"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="53"/>
-      <c r="B96" s="54"/>
-      <c r="C96" s="54"/>
+      <c r="A96" s="48"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="49"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="53"/>
-      <c r="B97" s="54"/>
-      <c r="C97" s="54"/>
+      <c r="A97" s="48"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="49"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="53"/>
-      <c r="B98" s="54"/>
-      <c r="C98" s="54"/>
+      <c r="A98" s="48"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="49"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="53"/>
-      <c r="B99" s="54"/>
-      <c r="C99" s="54"/>
+      <c r="A99" s="48"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="49"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="53"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="54"/>
+      <c r="A100" s="48"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="49"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="54"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="54"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="49"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="54"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="54"/>
+      <c r="A102" s="49"/>
+      <c r="B102" s="49"/>
+      <c r="C102" s="49"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="54"/>
-      <c r="B103" s="54"/>
-      <c r="C103" s="54"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="49"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="54"/>
-      <c r="B104" s="54"/>
-      <c r="C104" s="54"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="54"/>
-      <c r="B105" s="54"/>
-      <c r="C105" s="54"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="54"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="54"/>
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="49"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="54"/>
-      <c r="B107" s="54"/>
-      <c r="C107" s="54"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="54"/>
-      <c r="B108" s="54"/>
-      <c r="C108" s="54"/>
+      <c r="A108" s="49"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="49"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="54"/>
-      <c r="B109" s="54"/>
-      <c r="C109" s="54"/>
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="54"/>
-      <c r="B110" s="54"/>
-      <c r="C110" s="54"/>
+      <c r="A110" s="49"/>
+      <c r="B110" s="49"/>
+      <c r="C110" s="49"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="54"/>
-      <c r="B111" s="54"/>
-      <c r="C111" s="54"/>
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="54"/>
-      <c r="B112" s="54"/>
-      <c r="C112" s="54"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="49"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="54"/>
-      <c r="B113" s="54"/>
-      <c r="C113" s="54"/>
+      <c r="A113" s="49"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="49"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="54"/>
-      <c r="B114" s="54"/>
-      <c r="C114" s="54"/>
+      <c r="A114" s="49"/>
+      <c r="B114" s="49"/>
+      <c r="C114" s="49"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="54"/>
-      <c r="B115" s="54"/>
-      <c r="C115" s="54"/>
+      <c r="A115" s="49"/>
+      <c r="B115" s="49"/>
+      <c r="C115" s="49"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="54"/>
-      <c r="B116" s="54"/>
-      <c r="C116" s="54"/>
+      <c r="A116" s="49"/>
+      <c r="B116" s="49"/>
+      <c r="C116" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1863,13 +1774,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="42" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="12" t="s">
@@ -1911,13 +1822,13 @@
       <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="15" t="s">
@@ -2019,322 +1930,6 @@
       </c>
       <c r="E11" s="16" t="s">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="38.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="54.75" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="18">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A5" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A10" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A12" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A13" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A14" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A15" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A16" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A17" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A18" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
